--- a/artfynd/A 56549-2025 artfynd.xlsx
+++ b/artfynd/A 56549-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89601316</v>
+        <v>89601324</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422358.9139622988</v>
+        <v>422252</v>
       </c>
       <c r="R2" t="n">
-        <v>7014643.786633979</v>
+        <v>7014672</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89601315</v>
+        <v>89601316</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422358.9139622988</v>
+        <v>422359</v>
       </c>
       <c r="R3" t="n">
-        <v>7014643.786633979</v>
+        <v>7014644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89601324</v>
+        <v>89601320</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422252.1981991042</v>
+        <v>422449</v>
       </c>
       <c r="R4" t="n">
-        <v>7014672.047083055</v>
+        <v>7014515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89601320</v>
+        <v>89601315</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422449.2216842871</v>
+        <v>422359</v>
       </c>
       <c r="R5" t="n">
-        <v>7014514.979769911</v>
+        <v>7014644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 56549-2025 artfynd.xlsx
+++ b/artfynd/A 56549-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89601324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89601316</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89601320</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89601315</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>